--- a/dtm_dashboard/excel_data/keeping_prr/Зеленодольск Данафлекс/Июнь 2026.xlsx
+++ b/dtm_dashboard/excel_data/keeping_prr/Зеленодольск Данафлекс/Июнь 2026.xlsx
@@ -23,9 +23,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Остатки и обороты в тоннах по дням с 01.06.2026 по 03.06.2026</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+  <si>
+    <t>Остатки и обороты в тоннах по дням с 01.06.2026 по 08.06.2026</t>
   </si>
   <si>
     <t>Отбор:</t>
@@ -59,6 +59,21 @@
   </si>
   <si>
     <t>03.06.2026</t>
+  </si>
+  <si>
+    <t>04.06.2026</t>
+  </si>
+  <si>
+    <t>05.06.2026</t>
+  </si>
+  <si>
+    <t>06.06.2026</t>
+  </si>
+  <si>
+    <t>07.06.2026</t>
+  </si>
+  <si>
+    <t>08.06.2026</t>
   </si>
   <si>
     <t>Итого</t>
@@ -68,8 +83,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="50" formatCode=""/>
+    <numFmt numFmtId="51" formatCode="0.0"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -217,7 +233,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf/>
     <xf applyAlignment="true">
       <alignment horizontal="left"/>
@@ -249,13 +265,16 @@
     <xf numFmtId="2" borderId="2" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
+    <xf numFmtId="51" borderId="2" applyNumberFormat="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="right" vertical="top" wrapText="0"/>
+    </xf>
     <xf fontId="3" fillId="2" borderId="1" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="51" fontId="3" fillId="2" borderId="1" applyNumberFormat="true" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="top" wrapText="0"/>
     </xf>
     <xf fontId="3" fillId="2" borderId="5" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -292,7 +311,7 @@
     <outlinePr summaryBelow="false" summaryRight="false"/>
     <pageSetUpPr autoPageBreaks="false" fitToPage="false"/>
   </sheetPr>
-  <dimension ref="J10"/>
+  <dimension ref="J15"/>
   <sheetFormatPr defaultColWidth="10.5" customHeight="true" defaultRowHeight="11.429"/>
   <cols>
     <col min="1" max="1" width="8.66796875" style="1" customWidth="true"/>
@@ -415,26 +434,118 @@
       <c r="I9" s="8" t="e"/>
       <c r="J9" s="9" t="e"/>
     </row>
-    <row r="10" ht="13" customHeight="true">
-      <c r="A10" s="11" t="s">
+    <row r="10" ht="11" customHeight="true">
+      <c r="A10" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="11" t="e"/>
-      <c r="C10" s="11" t="e"/>
-      <c r="D10" s="12" t="n">
+      <c r="B10" s="5" t="e"/>
+      <c r="C10" s="5" t="e"/>
+      <c r="D10" s="6" t="n">
+        <v>308</v>
+      </c>
+      <c r="E10" s="7" t="e"/>
+      <c r="F10" s="10" t="n">
+        <v>793.75</v>
+      </c>
+      <c r="G10" s="10" t="e"/>
+      <c r="H10" s="7" t="e"/>
+      <c r="I10" s="8" t="e"/>
+      <c r="J10" s="9" t="e"/>
+    </row>
+    <row r="11" ht="11" customHeight="true">
+      <c r="A11" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="5" t="e"/>
+      <c r="C11" s="5" t="e"/>
+      <c r="D11" s="7" t="e"/>
+      <c r="E11" s="11" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="F11" s="10" t="n">
+        <v>749.25</v>
+      </c>
+      <c r="G11" s="10" t="e"/>
+      <c r="H11" s="7" t="e"/>
+      <c r="I11" s="8" t="e"/>
+      <c r="J11" s="9" t="e"/>
+    </row>
+    <row r="12" ht="11" customHeight="true">
+      <c r="A12" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="5" t="e"/>
+      <c r="C12" s="5" t="e"/>
+      <c r="D12" s="6" t="n">
+        <v>88</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F12" s="10" t="n">
+        <v>814.75</v>
+      </c>
+      <c r="G12" s="10" t="e"/>
+      <c r="H12" s="7" t="e"/>
+      <c r="I12" s="8" t="e"/>
+      <c r="J12" s="9" t="e"/>
+    </row>
+    <row r="13" ht="11" customHeight="true">
+      <c r="A13" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="5" t="e"/>
+      <c r="C13" s="5" t="e"/>
+      <c r="D13" s="7" t="e"/>
+      <c r="E13" s="6" t="n">
         <v>44</v>
       </c>
-      <c r="E10" s="13" t="n">
-        <v>286.25</v>
-      </c>
-      <c r="F10" s="14" t="e"/>
-      <c r="G10" s="15" t="e"/>
-      <c r="H10" s="16" t="e"/>
-      <c r="I10" s="17" t="e"/>
-      <c r="J10" s="18" t="e"/>
+      <c r="F13" s="10" t="n">
+        <v>770.75</v>
+      </c>
+      <c r="G13" s="10" t="e"/>
+      <c r="H13" s="7" t="e"/>
+      <c r="I13" s="8" t="e"/>
+      <c r="J13" s="9" t="e"/>
+    </row>
+    <row r="14" ht="11" customHeight="true">
+      <c r="A14" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="5" t="e"/>
+      <c r="C14" s="5" t="e"/>
+      <c r="D14" s="7" t="e"/>
+      <c r="E14" s="10" t="n">
+        <v>65.25</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>705.5</v>
+      </c>
+      <c r="G14" s="11" t="e"/>
+      <c r="H14" s="7" t="e"/>
+      <c r="I14" s="8" t="e"/>
+      <c r="J14" s="9" t="e"/>
+    </row>
+    <row r="15" ht="13" customHeight="true">
+      <c r="A15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="12" t="e"/>
+      <c r="C15" s="12" t="e"/>
+      <c r="D15" s="13" t="n">
+        <v>440</v>
+      </c>
+      <c r="E15" s="14" t="n">
+        <v>462.5</v>
+      </c>
+      <c r="F15" s="15" t="e"/>
+      <c r="G15" s="16" t="e"/>
+      <c r="H15" s="17" t="e"/>
+      <c r="I15" s="18" t="e"/>
+      <c r="J15" s="19" t="e"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="20">
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="I6:J6"/>
@@ -445,6 +556,16 @@
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="F9:G9"/>
     <mergeCell ref="A10:C10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
   <pageMargins left="0.393700787401574803149606299" top="0.393700787401574803149606299" right="0.393700787401574803149606299" bottom="0.393700787401574803149606299" header="0" footer="0"/>
   <pageSetup blackAndWhite="false" scale="100" pageOrder="overThenDown" orientation="portrait"/>
